--- a/data/trans_bre/P16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,8</t>
+          <t>-0,33; 0,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,83</t>
+          <t>-0,24; 0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,15</t>
+          <t>-1,43; 0,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,62</t>
+          <t>-0,33; 1,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-99,68; —</t>
+          <t>-78,01; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,51</t>
+          <t>-0,55; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,89</t>
+          <t>-0,45; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,44</t>
+          <t>-0,15; 1,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,86</t>
+          <t>-1,22; 0,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 525,23</t>
+          <t>-60,17; 586,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,57; 697,49</t>
+          <t>-46,26; 595,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,81; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,65; —</t>
+          <t>-89,35; 503,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,15</t>
+          <t>-1,14; 3,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,43</t>
+          <t>-2,64; 0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,05</t>
+          <t>-2,58; 1,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,52</t>
+          <t>-3,55; 0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 196,25</t>
+          <t>-36,92; 192,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,32; 53,45</t>
+          <t>-83,7; 51,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 60,03</t>
+          <t>-62,47; 53,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 23,28</t>
+          <t>-76,1; 18,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -1,31</t>
+          <t>-8,9; -0,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,9</t>
+          <t>-5,76; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -4,52</t>
+          <t>-11,23; -4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,68</t>
+          <t>-5,74; -0,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-65,89; -12,7</t>
+          <t>-66,12; -11,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 14,51</t>
+          <t>-56,07; 14,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-86,08; -50,3</t>
+          <t>-85,57; -49,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,05; -11,41</t>
+          <t>-61,35; -10,95</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,33</t>
+          <t>-8,61; 3,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 0,59</t>
+          <t>-10,23; 0,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -0,8</t>
+          <t>-12,6; -1,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -3,96</t>
+          <t>-13,19; -3,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 24,78</t>
+          <t>-41,32; 20,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 7,52</t>
+          <t>-54,73; 1,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -2,44</t>
+          <t>-53,88; -7,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,49; -31,1</t>
+          <t>-82,82; -28,77</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,63; -0,07</t>
+          <t>-15,77; -0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 0,45</t>
+          <t>-14,86; 0,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 7,86</t>
+          <t>-6,54; 7,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,81</t>
+          <t>-4,6; 5,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,94; -0,31</t>
+          <t>-46,51; -0,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 1,57</t>
+          <t>-42,68; 2,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 38,32</t>
+          <t>-24,39; 36,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 27,69</t>
+          <t>-16,94; 25,34</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,29; 0,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,57</t>
+          <t>-1,5; 0,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,52</t>
+          <t>-1,72; 0,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,78</t>
+          <t>-1,65; 0,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 20,74</t>
+          <t>-21,61; 18,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 12,51</t>
+          <t>-25,38; 14,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 9,55</t>
+          <t>-26,66; 13,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 15,99</t>
+          <t>-27,51; 16,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,76</t>
+          <t>-0,33; 0,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,78</t>
+          <t>-0,23; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,16</t>
+          <t>-1,29; 0,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,64</t>
+          <t>-0,41; 1,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,01; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,54%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,59</t>
+          <t>-0,58; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,89</t>
+          <t>-0,37; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,42</t>
+          <t>-0,04; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,83</t>
+          <t>-0,86; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 586,64</t>
+          <t>-63,21; 430,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 595,18</t>
+          <t>-51,09; 524,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-66,99; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 503,16</t>
+          <t>-78,73; inf</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-49,58%</t>
+          <t>-59,83%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,01</t>
+          <t>-1,18; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,54</t>
+          <t>-2,53; 0,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,01</t>
+          <t>-2,63; 1,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,41</t>
+          <t>-4,21; -0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 192,65</t>
+          <t>-37,14; 217,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,7; 51,0</t>
+          <t>-80,59; 52,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,47; 53,29</t>
+          <t>-65,09; 54,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 18,05</t>
+          <t>-80,57; -27,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-41,15%</t>
+          <t>-40,05%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -0,93</t>
+          <t>-8,6; -1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,9</t>
+          <t>-5,72; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -4,4</t>
+          <t>-11,2; -4,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,69</t>
+          <t>-5,49; -0,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,12; -11,73</t>
+          <t>-66,59; -11,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,07; 14,87</t>
+          <t>-56,19; 18,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-85,57; -49,24</t>
+          <t>-86,42; -50,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -10,95</t>
+          <t>-60,6; -10,86</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-58,48%</t>
+          <t>-33,62%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,0</t>
+          <t>-7,56; 3,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 0,17</t>
+          <t>-9,58; 0,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -1,34</t>
+          <t>-12,49; -1,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -3,47</t>
+          <t>-7,26; -1,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 20,01</t>
+          <t>-37,0; 29,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 1,69</t>
+          <t>-53,57; 8,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,88; -7,36</t>
+          <t>-53,21; -6,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,82; -28,77</t>
+          <t>-50,04; -9,37</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -0,05</t>
+          <t>-15,33; 0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 0,58</t>
+          <t>-14,83; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,55</t>
+          <t>-6,67; 7,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 5,36</t>
+          <t>-5,46; 4,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,51; -0,19</t>
+          <t>-44,48; 0,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 2,49</t>
+          <t>-43,05; 4,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 36,87</t>
+          <t>-24,49; 35,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 25,34</t>
+          <t>-19,08; 21,14</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-7,86%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,91</t>
+          <t>-1,29; 0,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,68</t>
+          <t>-1,54; 0,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,71</t>
+          <t>-1,74; 0,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,83</t>
+          <t>-1,37; 0,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 18,91</t>
+          <t>-20,98; 18,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 14,87</t>
+          <t>-26,39; 11,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 13,19</t>
+          <t>-26,7; 9,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 16,97</t>
+          <t>-21,32; 8,7</t>
         </is>
       </c>
     </row>
